--- a/src/archived data/New-release-old/Figure7.xlsx
+++ b/src/archived data/New-release-old/Figure7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\visualisations\dvc3400-3499\dvc3488-productivity-flash\fig7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\visualisations\dvc-semi-automated-bulletins\productivity-flash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD1E398-D4D9-404B-86A0-4844A7FC7F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691E2E0A-A3EB-4416-AE88-50F3D12CF0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25920" yWindow="-1965" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data for Dataviz" sheetId="2" r:id="rId1"/>
@@ -38,10 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
-    <t>Figure 7: Output per hour in the IT industry grew by 32%, compared with its 2019 average, because of a large increase in gross value added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 3 (Jul to Sep) 2025 compared with 2019 average, percentage change, UK </t>
+    <t>Figure 7: In 2025Q4 the IT industry saw output per hour grow by 35.7% in comparison with its 2019 average due to a large increase in GVA</t>
+  </si>
+  <si>
+    <t>Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 4 (Oct to Dec) 2025 compared with 2019 average, percentage change, UK</t>
   </si>
   <si>
     <t>Notes</t>
@@ -56,15 +56,15 @@
     <t>Industry</t>
   </si>
   <si>
+    <t>Output per hour worked</t>
+  </si>
+  <si>
     <t>GVA</t>
   </si>
   <si>
     <t>Hours worked</t>
   </si>
   <si>
-    <t>Output per hour worked</t>
-  </si>
-  <si>
     <t>Whole Economy excluding imputed rental</t>
   </si>
   <si>
@@ -104,7 +104,7 @@
     <t>L: Real Estate</t>
   </si>
   <si>
-    <t>M: Business Services</t>
+    <t>M: Professional, Scientific and Technical Activities</t>
   </si>
   <si>
     <t>N: Admin. Services</t>
@@ -503,376 +503,431 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F044E81-6507-406E-A706-F956F5590C89}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="13.2" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2.0055584926665402E-2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5.6230289574116597E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3.5463464130782697E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>5.8249889078513896E-2</v>
+        <v>0.24963448267983199</v>
       </c>
       <c r="C8" s="2">
-        <v>2.8929548994404797E-2</v>
+        <v>6.1361790975524799E-2</v>
       </c>
       <c r="D8" s="2">
-        <v>2.8495964677819299E-2</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-0.150662209080976</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>5.7185941306112806E-2</v>
+        <v>-0.23046145000232102</v>
       </c>
       <c r="C9" s="2">
-        <v>-0.13585731409433099</v>
+        <v>-0.38471265665575205</v>
       </c>
       <c r="D9" s="2">
-        <v>0.22339280138455903</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-0.20044636705191199</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>-0.38471265665575205</v>
+        <v>0.106708120570259</v>
       </c>
       <c r="C10" s="2">
-        <v>-0.138518313667438</v>
+        <v>3.25316820936059E-2</v>
       </c>
       <c r="D10" s="2">
-        <v>-0.285780123819456</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-6.7024391615047099E-2</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>4.6363257473401601E-2</v>
+        <v>-0.52809194438870699</v>
       </c>
       <c r="C11" s="2">
-        <v>-7.5203179315919091E-2</v>
+        <v>-0.47544669397814304</v>
       </c>
       <c r="D11" s="2">
-        <v>0.131452048785588</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.11155827874641601</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>-0.496503194145687</v>
+        <v>1.28314886206717E-2</v>
       </c>
       <c r="C12" s="2">
-        <v>6.2502992684060302E-2</v>
+        <v>0.16581718069868601</v>
       </c>
       <c r="D12" s="2">
-        <v>-0.52612198805916299</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.15104752744838001</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>0.159864578295323</v>
+        <v>3.1454626756101098E-2</v>
       </c>
       <c r="C13" s="2">
-        <v>0.11732006264510501</v>
+        <v>2.2814236743217798E-2</v>
       </c>
       <c r="D13" s="2">
-        <v>3.8077286063851599E-2</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-8.3768978186242703E-3</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>4.3753048424436801E-2</v>
+        <v>-6.5033264129262802E-3</v>
       </c>
       <c r="C14" s="2">
-        <v>-1.2763024621408301E-2</v>
+        <v>-8.3461185552265796E-2</v>
       </c>
       <c r="D14" s="2">
-        <v>5.7246714269562494E-2</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-7.7461617321252799E-2</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>-8.3698934956963594E-2</v>
+        <v>0.106713461087122</v>
       </c>
       <c r="C15" s="2">
-        <v>-6.9575341574596605E-2</v>
+        <v>0.10075814025003201</v>
       </c>
       <c r="D15" s="2">
-        <v>-1.5179728153668E-2</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-5.3810864749395107E-3</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>6.3099504429384001E-2</v>
+        <v>-3.56845009006099E-2</v>
       </c>
       <c r="C16" s="2">
-        <v>3.5865604306277699E-3</v>
+        <v>-2.6638569190036102E-2</v>
       </c>
       <c r="D16" s="2">
-        <v>5.9300260032597495E-2</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>9.3806764684607399E-3</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2">
-        <v>-3.4527476090128004E-2</v>
+        <v>0.35675577729562596</v>
       </c>
       <c r="C17" s="2">
-        <v>1.12631481173579E-2</v>
+        <v>0.42411554304893895</v>
       </c>
       <c r="D17" s="2">
-        <v>-4.5280621856668105E-2</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4.9647671954328398E-2</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>0.41109660795714603</v>
+        <v>-8.7192914431498195E-2</v>
       </c>
       <c r="C18" s="2">
-        <v>6.9070132195539508E-2</v>
+        <v>-7.6855326293384194E-2</v>
       </c>
       <c r="D18" s="2">
-        <v>0.31992894148037698</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1.13250524689734E-2</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2">
-        <v>-8.2818793177793795E-2</v>
+        <v>-0.11774224566913899</v>
       </c>
       <c r="C19" s="2">
-        <v>4.4803029975622098E-2</v>
+        <v>6.1071314773947602E-2</v>
       </c>
       <c r="D19" s="2">
-        <v>-0.122149170218613</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.20267723300284898</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2">
-        <v>6.0504856202131301E-2</v>
+        <v>0.14448503778532601</v>
       </c>
       <c r="C20" s="2">
-        <v>0.2123980669146</v>
+        <v>0.23555741193337301</v>
       </c>
       <c r="D20" s="2">
-        <v>-0.125283283483796</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>7.9574980136289206E-2</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2">
-        <v>0.27147832271246902</v>
+        <v>0.10858002908243999</v>
       </c>
       <c r="C21" s="2">
-        <v>8.8277027854151993E-2</v>
+        <v>0.10935492269318299</v>
       </c>
       <c r="D21" s="2">
-        <v>0.16834067996413601</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6.9899654550309399E-4</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2">
-        <v>0.113218163952599</v>
+        <v>6.2573252225310806E-3</v>
       </c>
       <c r="C22" s="2">
-        <v>-1.5186752757442501E-2</v>
+        <v>0.17699200988831498</v>
       </c>
       <c r="D22" s="2">
-        <v>0.130385042107802</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.169672985613323</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2">
-        <v>0.17017613561117698</v>
+        <v>-6.5642398724706202E-2</v>
       </c>
       <c r="C23" s="2">
-        <v>0.16999752575847499</v>
+        <v>1.42018015181977E-2</v>
       </c>
       <c r="D23" s="2">
-        <v>1.5265831659427799E-4</v>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8.5453578088223903E-2</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>4.6368703092916297E-2</v>
+        <v>-0.13446117605028302</v>
       </c>
       <c r="C24" s="2">
-        <v>6.0078750976112899E-2</v>
+        <v>5.1043885811674398E-2</v>
       </c>
       <c r="D24" s="2">
-        <v>-1.2933046597314299E-2</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.21432321315806699</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+    </row>
+    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>4.1727027410879101E-2</v>
+        <v>-6.2997631627842207E-2</v>
       </c>
       <c r="C25" s="2">
-        <v>0.16027883730341799</v>
+        <v>3.6552678860711098E-2</v>
       </c>
       <c r="D25" s="2">
-        <v>-0.102175275529512</v>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.106243392598356</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+    </row>
+    <row r="26" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2">
-        <v>3.4196341786692598E-2</v>
+        <v>-4.8770812133831901E-2</v>
       </c>
       <c r="C26" s="2">
-        <v>5.3557231261418294E-2</v>
+        <v>-3.4851026628547103E-2</v>
       </c>
       <c r="D26" s="2">
-        <v>-1.8376685100955501E-2</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="2">
-        <v>-6.5094629397726991E-2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>2.17895372542962E-2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>-8.5031372395429003E-2</v>
-      </c>
+        <v>1.4633471809785501E-2</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -881,6 +936,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7387ef7178ec9fe6b285910e58c20d0b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fee36ab1686691439382caeb7e5f0351" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
@@ -1129,7 +1193,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
@@ -1140,17 +1204,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD18BD6C-5E00-4920-98BC-7E7255DB54D7}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C0A0A48-3A3C-4B59-8612-EFA492E9307D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1168,7 +1231,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1177,12 +1240,4 @@
     <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>